--- a/Pruebas calificadas/COLEGIO FILARMÓNICO JORGE MARIO BERGOGLIO-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO FILARMÓNICO JORGE MARIO BERGOGLIO-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1008,11 +1004,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -1020,7 +1012,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1201,11 +1193,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -1213,7 +1201,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1454,11 +1442,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -1466,7 +1450,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1707,11 +1691,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -1719,7 +1699,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1960,11 +1940,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -1972,7 +1948,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2213,11 +2189,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -2225,7 +2197,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2466,11 +2438,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -2478,7 +2446,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2719,11 +2687,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -2731,7 +2695,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2972,11 +2936,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -2984,7 +2944,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3225,11 +3185,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -3237,7 +3193,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3478,11 +3434,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -3490,7 +3442,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3731,11 +3683,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -3743,7 +3691,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3984,11 +3932,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -3996,7 +3940,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4233,11 +4177,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -4245,7 +4185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4486,11 +4426,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -4498,7 +4434,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4739,11 +4675,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -4751,7 +4683,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4992,11 +4924,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -5004,7 +4932,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5245,11 +5173,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -5257,7 +5181,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5498,11 +5422,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -5510,7 +5430,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5751,11 +5671,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -5763,7 +5679,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6004,11 +5920,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -6016,7 +5928,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6257,11 +6169,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -6269,7 +6177,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6510,11 +6418,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -6522,7 +6426,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6763,11 +6667,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -6775,7 +6675,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7016,11 +6916,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -7028,7 +6924,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7269,11 +7165,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -7281,7 +7173,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7522,11 +7414,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -7534,7 +7422,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7775,11 +7663,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -7787,7 +7671,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8028,11 +7912,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -8040,7 +7920,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8281,11 +8161,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -8293,7 +8169,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8534,11 +8410,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -8546,7 +8418,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8787,11 +8659,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -8799,7 +8667,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9040,11 +8908,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -9052,7 +8916,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9293,11 +9157,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -9305,7 +9165,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9494,11 +9354,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -9506,7 +9362,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9747,11 +9603,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -9759,7 +9611,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10000,11 +9852,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -10012,7 +9860,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10253,11 +10101,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -10265,7 +10109,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10502,11 +10346,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -10514,7 +10354,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10755,11 +10595,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -10767,7 +10603,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11008,11 +10844,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -11020,7 +10852,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11261,11 +11093,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -11273,7 +11101,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11514,11 +11342,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -11526,7 +11350,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11767,11 +11591,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -11779,7 +11599,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12020,11 +11840,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -12032,7 +11848,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12273,11 +12089,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -12285,7 +12097,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12526,11 +12338,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -12538,7 +12346,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12779,11 +12587,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -12791,7 +12595,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -12964,11 +12768,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -12976,7 +12776,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOLIO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13157,11 +12957,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -13169,7 +12965,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13410,11 +13206,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -13422,7 +13214,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13663,11 +13455,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -13675,7 +13463,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -13916,11 +13704,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -13928,7 +13712,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14169,11 +13953,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -14181,7 +13961,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14422,11 +14202,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -14434,7 +14210,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14675,11 +14451,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -14687,7 +14459,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -14928,11 +14700,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -14940,7 +14708,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15181,11 +14949,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -15193,7 +14957,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BEROGGLIO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15362,11 +15126,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -15374,7 +15134,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15535,11 +15295,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -15547,7 +15303,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -15716,11 +15472,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -15728,7 +15480,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -15893,11 +15645,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -15905,7 +15653,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BEROGOLIO</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16142,11 +15890,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -16154,7 +15898,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16395,11 +16139,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -16407,7 +16147,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -16648,11 +16388,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -16660,7 +16396,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -16901,11 +16637,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -16913,7 +16645,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17154,11 +16886,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800163</t>
@@ -17166,7 +16894,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FILARMONICO JORGE MARIO BERGOGLIO (IED)</t>
+          <t>FILARMONICO JORGE MARIO BERGOGLIO</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
